--- a/sources/trueogre_step3.xlsx
+++ b/sources/trueogre_step3.xlsx
@@ -685,6 +685,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>2db4eeef-b4fe-480b-b0d5-23cc4073a254</t>
@@ -722,6 +727,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>662f3084-8c10-4530-80ac-0d54755abd83</t>
@@ -757,6 +767,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1099d7d4-6a6d-45ae-81cf-93df73c48ae4</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
